--- a/results/Int Task Remove ACC -0.6/Rando_2_permute.xlsx
+++ b/results/Int Task Remove ACC -0.6/Rando_2_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7022229824549155</v>
+        <v>0.6976565827230139</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6933708484895029</v>
+        <v>0.6999890037771153</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.679615097290391</v>
+        <v>0.7067146776884892</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6835171855254798</v>
+        <v>0.7162503229049577</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6952471881087194</v>
+        <v>0.712558733793662</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6993597754676013</v>
+        <v>0.6955606677325439</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6967466889151092</v>
+        <v>0.6888700770084688</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6931908944292786</v>
+        <v>0.6779333733619118</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6823334334047797</v>
+        <v>0.6822168385335576</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6784686974188548</v>
+        <v>0.7000286250881443</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6784686974188548</v>
+        <v>0.7018744196437923</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6815333272825017</v>
+        <v>0.7037643736341993</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6815333272825017</v>
+        <v>0.7052287912532902</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.675897501239257</v>
+        <v>0.7095099873630708</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7091275631671914</v>
+        <v>0.7221193386906466</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7079811632956553</v>
+        <v>0.7221193386906466</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7087383317857168</v>
+        <v>0.7211438166318744</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7120745509002939</v>
+        <v>0.7124342844775223</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.711943294398559</v>
+        <v>0.7018789577675224</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.695274591394321</v>
+        <v>0.679271072602998</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6932251049004754</v>
+        <v>0.6793061557902969</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7015724598725136</v>
+        <v>0.6793061557902969</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6574034252361569</v>
+        <v>0.6933029511767703</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6600606712234083</v>
+        <v>0.6931275352402761</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6584276448534185</v>
+        <v>0.7164721673380763</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6848356850123227</v>
+        <v>0.7120811835426688</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6842788921392715</v>
+        <v>0.7183858592064567</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6790923403453164</v>
+        <v>0.7137255552219841</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6759224609197729</v>
+        <v>0.7158282773980493</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6403114549224679</v>
+        <v>0.7203924080680858</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6737631867403007</v>
+        <v>0.6885770189414302</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6603628055379073</v>
+        <v>0.6857557023270102</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6593567384155665</v>
+        <v>0.6815752176553957</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6640114570169866</v>
+        <v>0.7017714391437608</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.69268419546048</v>
+        <v>0.6809878797187761</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6686131144794074</v>
+        <v>0.680561121544917</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6636766831202743</v>
+        <v>0.680561121544917</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6639901627440987</v>
+        <v>0.6748200459397756</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6497919444812925</v>
+        <v>0.6895185050722259</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6493053179828389</v>
+        <v>0.721299858270905</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6676047782952015</v>
+        <v>0.7219732460151782</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6676047782952015</v>
+        <v>0.7221814760771061</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6764455669512884</v>
+        <v>0.6662293777185107</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6684773198539422</v>
+        <v>0.6691231297693936</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6434612618776662</v>
+        <v>0.6691231297693936</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6561248961467839</v>
+        <v>0.6721537237050639</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6588036109501435</v>
+        <v>0.6719828458922998</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6365341650899595</v>
+        <v>0.6748448310770713</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6579424147007282</v>
+        <v>0.6627596330403335</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6604830658167575</v>
+        <v>0.7281512033009614</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6689028562252585</v>
+        <v>0.7193184436330124</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.646013258303021</v>
+        <v>0.7152590919563502</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.6542949850241917</v>
+        <v>0.7117711947832522</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.6812666252417423</v>
+        <v>0.6779471622763229</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.6380800943929736</v>
+        <v>0.6776687658397973</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.6380800943929736</v>
+        <v>0.7093923452325265</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.6556473458957907</v>
+        <v>0.7255007644993053</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.6616713560611879</v>
+        <v>0.7196567083941325</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.6616713560611879</v>
+        <v>0.7229341064434376</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.6616713560611879</v>
+        <v>0.7130521674777108</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.6711300277174634</v>
+        <v>0.7257452995510749</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.7150554000181526</v>
+        <v>0.7389182509372971</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.6879434270514064</v>
+        <v>0.7232364153011569</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.7227442034196507</v>
+        <v>0.6867654348569793</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.7184256550607061</v>
+        <v>0.6088371232484587</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.7295229384700239</v>
+        <v>0.6175421172790807</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.7295229384700239</v>
+        <v>0.6067548226291795</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.739545210184946</v>
+        <v>0.6100955798674867</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.739545210184946</v>
+        <v>0.60985226661826</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.7282079298475889</v>
+        <v>0.5953779209807932</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.7457072840376735</v>
+        <v>0.6378208977106912</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.7121831167833779</v>
+        <v>0.628846583491004</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.7149908190266074</v>
+        <v>0.628846583491004</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.7443140800525025</v>
+        <v>0.6185832675887204</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.751065760903715</v>
+        <v>0.6280396701831308</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.7538497252689711</v>
+        <v>0.6281731957467308</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.7504602704721743</v>
+        <v>0.6327305192311721</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.6967377872108691</v>
+        <v>0.6221242259008175</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.668929735881199</v>
+        <v>0.5310128393992921</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.6534753300612297</v>
+        <v>0.5453218926070473</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.6094932312139132</v>
+        <v>0.49915451264042</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.6097794820953564</v>
+        <v>0.49915451264042</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5557606244458253</v>
+        <v>0.4977976136450908</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5332874866474436</v>
+        <v>0.4991918648895839</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.537849348255615</v>
+        <v>0.5036982217536706</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5999554914788</v>
+        <v>0.5003993548882574</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.6620288205765511</v>
+        <v>0.4948823927780997</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5298495088353778</v>
+        <v>0.4979164775781779</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.498952042504765</v>
+        <v>0.4974343892034546</v>
       </c>
     </row>
   </sheetData>
